--- a/product_upload/packages/50/file.xlsx
+++ b/product_upload/packages/50/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -840,6 +845,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Gizamlo</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-06C113EFE989</t>
         </is>
       </c>
@@ -863,7 +873,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1030,6 +1040,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>Gizamlo</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-39D3489F0D69</t>
         </is>
       </c>
@@ -1053,7 +1068,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1224,6 +1239,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>Gizamlo</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-F0944834948C</t>
         </is>
       </c>
@@ -1247,7 +1267,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1418,6 +1438,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>LYPFEN</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-0BB1A9C5F207</t>
         </is>
       </c>
@@ -1441,7 +1466,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1612,6 +1637,11 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Formit XR</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-2816DACF6672</t>
         </is>
       </c>
@@ -1635,7 +1665,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1802,6 +1832,11 @@
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Bilaxten</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-8970BFD2B0FA</t>
         </is>
       </c>
@@ -1825,7 +1860,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1996,6 +2031,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Bilaxten</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-9C943A553F3F</t>
         </is>
       </c>
@@ -2019,7 +2059,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2186,6 +2226,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>KAPRON</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-336E0E32BE06</t>
         </is>
       </c>
@@ -2209,7 +2254,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2372,6 +2417,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-E935A2B63BC9</t>
         </is>
       </c>
@@ -2395,7 +2445,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2558,6 +2608,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-CF26A90CE887</t>
         </is>
       </c>
@@ -2581,7 +2636,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2740,6 +2795,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-DC028D55FA91</t>
         </is>
       </c>
@@ -2763,7 +2823,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2930,6 +2990,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>Cartiflex</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-74DED215BAF8</t>
         </is>
       </c>
@@ -2953,7 +3018,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3120,6 +3185,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>Epnone</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-BB331982B0F6</t>
         </is>
       </c>
@@ -3143,7 +3213,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3310,6 +3380,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>Rastor</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-1105DD3831C9</t>
         </is>
       </c>
@@ -3333,7 +3408,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3504,6 +3579,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>Rastor</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-727FC48ED0AA</t>
         </is>
       </c>
@@ -3527,7 +3607,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3686,6 +3766,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>Rastor</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-74922BBF14D3</t>
         </is>
       </c>
@@ -3709,7 +3794,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3868,6 +3953,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>Rastor</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-7DD992340456</t>
         </is>
       </c>
@@ -3891,7 +3981,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4046,6 +4136,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>Correx</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-4063AF509939</t>
         </is>
       </c>
@@ -4069,7 +4164,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4236,6 +4331,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ATECTURA 150/160MCG INHALATION POWDER,HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-2C72E47454D0</t>
         </is>
       </c>
@@ -4259,7 +4359,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4422,6 +4522,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ATECTURA</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-A71C569ACEF8</t>
         </is>
       </c>
@@ -4445,7 +4550,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4612,6 +4717,11 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ATECTURA</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-6435A484844C</t>
         </is>
       </c>
@@ -4635,7 +4745,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4798,6 +4908,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>AVOCOM 0.1% OINTMENT 50 g</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-CF02FB5D2C13</t>
         </is>
       </c>
@@ -4821,7 +4936,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4992,6 +5107,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>ELIVE</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-D12D88902817</t>
         </is>
       </c>
@@ -5015,7 +5135,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5174,6 +5294,11 @@
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>ELIVE</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-00D31937F680</t>
         </is>
       </c>
@@ -5197,7 +5322,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5360,6 +5485,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>Tadafect</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-CDD4052AA684</t>
         </is>
       </c>
@@ -5383,7 +5513,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5542,6 +5672,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t xml:space="preserve">GLOFEL 5 mg Film-coated Tablet	</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-58491520D393</t>
         </is>
       </c>
@@ -5565,7 +5700,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5736,6 +5871,11 @@
       </c>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Kerendia</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-0638DD89525A</t>
         </is>
       </c>
@@ -5759,7 +5899,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5926,6 +6066,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Opsumit</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-DEA5AF33AB98</t>
         </is>
       </c>
@@ -5949,7 +6094,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6124,6 +6269,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>DIBASA</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-5603E1A187C9</t>
         </is>
       </c>
@@ -6147,7 +6297,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6318,6 +6468,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Utrogestan</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-63E934B47DD3</t>
         </is>
       </c>
@@ -6341,7 +6496,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6508,6 +6663,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Utrogestan</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-DDD460BB301F</t>
         </is>
       </c>
@@ -6531,7 +6691,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6692,6 +6852,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Fenido</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-54D70F612B74</t>
         </is>
       </c>
@@ -6715,7 +6880,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6880,6 +7045,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Fenido</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-AE1B5E3CDC6B</t>
         </is>
       </c>
@@ -6903,7 +7073,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7078,6 +7248,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Breztri Aerosphere</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-1BFE0A91FA8E</t>
         </is>
       </c>
@@ -7101,7 +7276,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7264,6 +7439,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Tysabri</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-94E266CF36A9</t>
         </is>
       </c>
@@ -7287,7 +7467,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7450,6 +7630,11 @@
       </c>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>TAMFREX</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-4F100D0FB4CF</t>
         </is>
       </c>
@@ -7473,7 +7658,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7648,6 +7833,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>SOCLAV</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-CE2167DABB75</t>
         </is>
       </c>
@@ -7671,7 +7861,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7834,6 +8024,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>SOCLAV</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-CEF6C39F0257</t>
         </is>
       </c>
@@ -7857,7 +8052,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -8020,6 +8215,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-166FA262D3BE</t>
         </is>
       </c>
@@ -8043,7 +8243,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8202,6 +8402,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-C9777204B71C</t>
         </is>
       </c>
@@ -8225,7 +8430,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8388,6 +8593,11 @@
       </c>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-FF589A336CD0</t>
         </is>
       </c>
@@ -8411,7 +8621,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8578,6 +8788,11 @@
       </c>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>ASACOL</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-321AA16777BD</t>
         </is>
       </c>
@@ -8601,7 +8816,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8772,6 +8987,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Kerasal</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-0E02CB67E578</t>
         </is>
       </c>
@@ -8795,7 +9015,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8954,6 +9174,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Truvelog</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-A1351C2F89F7</t>
         </is>
       </c>
@@ -8977,7 +9202,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9144,6 +9369,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Dapazin</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-4C814C3B06F4</t>
         </is>
       </c>
@@ -9167,7 +9397,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9338,6 +9568,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Dapazin</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-A37AB3962C1F</t>
         </is>
       </c>
@@ -9361,7 +9596,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9536,6 +9771,11 @@
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>AKLIEF</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-0499C10606CD</t>
         </is>
       </c>
@@ -9559,7 +9799,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9730,6 +9970,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>Rosacil</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-4047931F5F56</t>
         </is>
       </c>
@@ -9753,7 +9998,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9920,6 +10165,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>Rosacil</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-7BF42FCD2463</t>
         </is>
       </c>
@@ -9943,7 +10193,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10098,6 +10348,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Tadalo</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-69AC19C39A73</t>
         </is>
       </c>
@@ -10121,7 +10376,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10288,6 +10543,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ENOXA</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-36264FEA47A7</t>
         </is>
       </c>
@@ -10311,7 +10571,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10474,6 +10734,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ENOXA</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-FA4A719E93FA</t>
         </is>
       </c>
@@ -10497,7 +10762,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10664,6 +10929,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ENOXA</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-C695B4931B1F</t>
         </is>
       </c>
@@ -10687,7 +10957,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Tunisia</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10854,6 +11124,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>ENOXA</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-A983E2177534</t>
         </is>
       </c>
@@ -10877,7 +11152,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11052,6 +11327,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Dapxiga</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-93F25548A433</t>
         </is>
       </c>
@@ -11075,7 +11355,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11242,6 +11522,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Dapxiga</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-333456E56071</t>
         </is>
       </c>
@@ -11265,7 +11550,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11436,6 +11721,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Bivoneb</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-082D85901221</t>
         </is>
       </c>
@@ -11459,7 +11749,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11638,6 +11928,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Glucovance</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-8EE8939A0E2C</t>
         </is>
       </c>
@@ -11661,7 +11956,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11828,6 +12123,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Valgiver</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-EDC2DB3E2892</t>
         </is>
       </c>
@@ -11851,7 +12151,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12030,6 +12330,11 @@
       </c>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Staquis</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-009F8C71E5DD</t>
         </is>
       </c>
@@ -12053,7 +12358,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12224,6 +12529,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>Xcard</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-E0CD413434DB</t>
         </is>
       </c>
@@ -12247,7 +12557,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12414,6 +12724,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>Xcard</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-7206B09ACD4C</t>
         </is>
       </c>
@@ -12437,7 +12752,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12604,6 +12919,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>Xcard</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-80582253DC0D</t>
         </is>
       </c>
@@ -12627,7 +12947,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12794,6 +13114,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>Xcard</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-011614C88FB4</t>
         </is>
       </c>
@@ -12817,7 +13142,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12984,6 +13309,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>Tofibra</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-71931A023C39</t>
         </is>
       </c>
@@ -13007,7 +13337,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13170,6 +13500,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>DIVAD 5000 I.U CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-7B798DDE3096</t>
         </is>
       </c>
@@ -13193,7 +13528,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13366,6 +13701,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>VaxigripTetra</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-710DD01A0812</t>
         </is>
       </c>
@@ -13389,7 +13729,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13548,6 +13888,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Orziban</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-34136498EFD0</t>
         </is>
       </c>
@@ -13571,7 +13916,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13730,6 +14075,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Vesuv</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-3550855741AD</t>
         </is>
       </c>
@@ -13753,7 +14103,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13916,6 +14266,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Vesuv</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-50F0CDF4CD80</t>
         </is>
       </c>
@@ -13939,7 +14294,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14110,6 +14465,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Sitagen</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-8CC42644BCE2</t>
         </is>
       </c>
@@ -14133,7 +14493,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14304,6 +14664,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Sitagen</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-B503184ADB1D</t>
         </is>
       </c>
@@ -14327,7 +14692,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Serbia</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14494,6 +14859,11 @@
       </c>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Zenix</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-DF36A10F380A</t>
         </is>
       </c>
@@ -14517,7 +14887,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14674,6 +15044,11 @@
       <c r="AS75" t="inlineStr"/>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Lovera</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-6226BA04FE74</t>
         </is>
       </c>
@@ -14697,7 +15072,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14856,6 +15231,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Posacore</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-68F5C3D0436E</t>
         </is>
       </c>
@@ -14879,7 +15259,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15046,6 +15426,11 @@
       </c>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Orladeyo</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-23D5E60DD5A0</t>
         </is>
       </c>
@@ -15069,7 +15454,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15240,6 +15625,11 @@
       <c r="AS78" t="inlineStr"/>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>BIMZELX</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-AC21424692F7</t>
         </is>
       </c>
@@ -15263,7 +15653,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15438,6 +15828,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-E0A67933F084</t>
         </is>
       </c>
@@ -15461,7 +15856,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15624,6 +16019,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>YUPELRI 175 mcg / 3 ml</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-EFBB0B4A5760</t>
         </is>
       </c>
@@ -15647,7 +16047,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15810,6 +16210,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>YUPELRI 175 mcg / 3 ml</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-8CB0C1A1E345</t>
         </is>
       </c>
@@ -15833,7 +16238,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16004,6 +16409,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Adazio</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-9D1569B3F82D</t>
         </is>
       </c>
@@ -16027,7 +16437,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16180,6 +16590,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Betaquil</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-9075B0DF6933</t>
         </is>
       </c>
@@ -16203,7 +16618,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16364,6 +16779,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Betaquil</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-23482E8F6D98</t>
         </is>
       </c>
@@ -16387,7 +16807,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16544,6 +16964,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Betaquil</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-F8798EDE06DE</t>
         </is>
       </c>
@@ -16567,7 +16992,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16736,6 +17161,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-F160F5CD3584</t>
         </is>
       </c>
@@ -16759,7 +17189,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16930,6 +17360,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-ED73F45E0945</t>
         </is>
       </c>
@@ -16953,7 +17388,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17122,6 +17557,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>Helt</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-3C7FD2904C98</t>
         </is>
       </c>
@@ -17145,7 +17585,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17312,6 +17752,11 @@
       <c r="AS89" t="inlineStr"/>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>Gleptal</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-F49A4CFE2B74</t>
         </is>
       </c>
@@ -17335,7 +17780,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17492,6 +17937,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>Xivar</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-DC7DD59462C7</t>
         </is>
       </c>
@@ -17515,7 +17965,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17680,6 +18130,11 @@
       </c>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>Iksaront</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-BD9BB59A249E</t>
         </is>
       </c>
@@ -17703,7 +18158,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17864,6 +18319,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Iksaront</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-95383178541C</t>
         </is>
       </c>
@@ -17887,7 +18347,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18050,6 +18510,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Neutra</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-274A5E0CF64E</t>
         </is>
       </c>
@@ -18073,7 +18538,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18238,6 +18703,11 @@
       </c>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Sorafenib BOS</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-DC12B154CEB8</t>
         </is>
       </c>
@@ -18261,7 +18731,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18422,6 +18892,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>Varlin</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-F7A7B02DA221</t>
         </is>
       </c>
@@ -18445,7 +18920,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18608,6 +19083,11 @@
       </c>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Varlin  0.5 mg 11 tablets + 1 mg 14 tablets</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-653C484200F4</t>
         </is>
       </c>
@@ -18631,7 +19111,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18800,6 +19280,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Wetzo</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-02285583DDFB</t>
         </is>
       </c>
@@ -18823,7 +19308,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18988,6 +19473,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Wetzo 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-C9F184C1FD28</t>
         </is>
       </c>
@@ -19011,7 +19501,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19182,6 +19672,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Aimovig</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-14DB869AD983</t>
         </is>
       </c>
@@ -19205,7 +19700,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19372,6 +19867,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Rivax</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-3B00F206B7FC</t>
         </is>
       </c>
@@ -19395,7 +19895,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19565,6 +20065,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Rivax</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-3FBE087317F6</t>
         </is>
@@ -19581,7 +20086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19627,100 +20132,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19752,7 +20262,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19767,92 +20277,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-26690</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>473.83</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>486</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19884,7 +20399,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19899,92 +20414,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-72951</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>114.13</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>487</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20016,7 +20536,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20031,92 +20551,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-65449</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>103.42</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>488</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20148,7 +20673,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20163,92 +20688,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-81302</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>158.71</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>489</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20280,7 +20810,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20295,92 +20825,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-52873</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>26.75</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>490</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20412,7 +20947,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20427,92 +20962,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-90066</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>245.54</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>491</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20544,7 +21084,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20559,92 +21099,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-52566</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>468.43</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>492</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20676,7 +21221,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20691,92 +21236,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-14013</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>398.94</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>493</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20808,7 +21358,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20823,92 +21373,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-13021</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>107.45</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>494</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20940,7 +21495,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20955,92 +21510,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-34968</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>251.54</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>495</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21072,7 +21632,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21087,92 +21647,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-13665</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>419.89</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>496</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21189,7 +21754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21295,6 +21860,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21330,7 +21905,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21395,6 +21970,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-8B74E2AEB705</t>
         </is>
@@ -21431,7 +22016,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21496,6 +22081,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-76BC6EC4D070</t>
         </is>
@@ -21532,7 +22127,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21597,6 +22192,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-AE15549FB641</t>
         </is>
@@ -21633,7 +22238,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21698,6 +22303,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-54405044ACE2</t>
         </is>
@@ -21734,7 +22349,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21799,6 +22414,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-37BB8F1B1BFE</t>
         </is>
@@ -21835,7 +22460,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21900,6 +22525,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-A2B0DBB09876</t>
         </is>
@@ -21936,7 +22571,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22001,6 +22636,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-8F74DC9D5602</t>
         </is>
@@ -22037,7 +22682,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22102,6 +22747,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-C39DD042803C</t>
         </is>
@@ -22138,7 +22793,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22203,6 +22858,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-3301F721A47B</t>
         </is>
@@ -22239,7 +22904,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22304,6 +22969,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-5841D802C2CB</t>
         </is>
@@ -22340,7 +23015,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22405,6 +23080,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-6F556DF76845</t>
         </is>
@@ -22441,7 +23126,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22506,6 +23191,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-844359CAC3A9</t>
         </is>
@@ -22542,7 +23237,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22607,6 +23302,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-18EC095DF4EC</t>
         </is>
@@ -22643,7 +23348,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22708,6 +23413,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-A12FD4D0CA00</t>
         </is>
@@ -22744,7 +23459,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22809,6 +23524,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-CEA9A988E74D</t>
         </is>
@@ -22845,7 +23570,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22910,6 +23635,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-E112D72A2245</t>
         </is>
@@ -22946,7 +23681,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23011,6 +23746,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-69BAE6FA2FE6</t>
         </is>
@@ -23047,7 +23792,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23112,6 +23857,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-CB9386B3BFE6</t>
         </is>
@@ -23148,7 +23903,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23213,6 +23968,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-9AF661A510F3</t>
         </is>
@@ -23249,7 +24014,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23314,6 +24079,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-17E80B85E107</t>
         </is>

--- a/product_upload/packages/50/file.xlsx
+++ b/product_upload/packages/50/file.xlsx
@@ -2262,8 +2262,16 @@
           <t>1975036807-753-094783153888</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>TRANSLARNA detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2453,8 +2461,16 @@
           <t>4896487957-863-411083230222</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>TRANSLARNA detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2644,8 +2660,16 @@
           <t>3085106402-840-881738529342</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRANSLARNA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>TRANSLARNA detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2831,8 +2855,16 @@
           <t>8820979017-429-463941311858</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Cartiflex</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Cartiflex detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -3026,8 +3058,16 @@
           <t>8525867874-330-047007714178</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Epnone</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Epnone detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3615,8 +3655,16 @@
           <t>2269485556-870-752917048658</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rastor</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Rastor detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3802,8 +3850,16 @@
           <t>0193526525-744-290687295119</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rastor</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Rastor detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3989,8 +4045,16 @@
           <t>7381492207-792-941793724225</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Correx</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Correx detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4172,8 +4236,16 @@
           <t>4667339610-359-435531130493</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATECTURA 150/160MCG INHALATION POWDER,HARD CAPSULE</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ATECTURA 150/160MCG INHALATION POWDER,HARD CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4367,8 +4439,16 @@
           <t>9392638896-002-525825483363</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATECTURA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ATECTURA detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4558,8 +4638,16 @@
           <t>4931479381-063-691679198619</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ATECTURA</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ATECTURA detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4753,8 +4841,16 @@
           <t>2398327446-403-131465589168</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ AVOCOM 0.1% OINTMENT 50 g</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>AVOCOM 0.1% OINTMENT 50 g detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -5143,8 +5239,16 @@
           <t>7393605242-535-855549368269</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ELIVE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>ELIVE detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5330,8 +5434,16 @@
           <t>8444936563-282-906063302762</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadafect</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Tadafect detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5521,8 +5633,16 @@
           <t>2347588424-719-802887117859</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ GLOFEL 5 mg Film-coated Tablet</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>GLOFEL 5 mg Film-coated Tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5907,8 +6027,16 @@
           <t>8409393417-354-368807876652</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Opsumit</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Opsumit detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -6699,8 +6827,16 @@
           <t>8015846191-045-549934197990</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fenido</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fenido detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -6888,8 +7024,16 @@
           <t>8288282126-720-402869196458</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Fenido</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fenido detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -7284,8 +7428,16 @@
           <t>2415521803-882-185784850813</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tysabri</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Tysabri detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="n">
         <v>0</v>
       </c>
@@ -7475,8 +7627,16 @@
           <t>8894012094-703-008245801202</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TAMFREX</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TAMFREX detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7869,8 +8029,16 @@
           <t>0912283244-844-683127163588</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SOCLAV</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>SOCLAV detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -8060,8 +8228,16 @@
           <t>7173548539-674-058409518890</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -8251,8 +8427,16 @@
           <t>6922661618-079-774432484384</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8438,8 +8622,16 @@
           <t>9228615859-557-419323435666</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dacarbazine medac</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Dacarbazine medac detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8629,8 +8821,16 @@
           <t>9297179062-888-141824960291</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ASACOL</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>ASACOL detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -9023,8 +9223,16 @@
           <t>1056041710-406-996185273374</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Truvelog</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Truvelog detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -10201,8 +10409,16 @@
           <t>0447746033-027-434627959025</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Tadalo</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Tadalo detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -10384,8 +10600,16 @@
           <t>6243925538-755-125744157705</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENOXA</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ENOXA detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10579,8 +10803,16 @@
           <t>4307775904-212-650321612727</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENOXA</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ENOXA detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10770,8 +11002,16 @@
           <t>5156698894-603-675284042985</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENOXA</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ENOXA detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10965,8 +11205,16 @@
           <t>7836757159-680-197832757874</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENOXA</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>ENOXA detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -11964,8 +12212,16 @@
           <t>3072568348-821-953282777541</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Valgiver</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Valgiver detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -12760,8 +13016,16 @@
           <t>5371142011-235-649603142321</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xcard</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Xcard detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12955,8 +13219,16 @@
           <t>1691256554-591-191738010384</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xcard</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Xcard detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
@@ -13345,8 +13617,16 @@
           <t>5767863747-516-940383153591</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ DIVAD 5000 I.U CAPSULE</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>DIVAD 5000 I.U CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -13737,8 +14017,16 @@
           <t>5329080441-590-859213348155</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Orziban</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Orziban detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t xml:space="preserve">MS Pharma Saudi </t>
@@ -13924,8 +14212,16 @@
           <t>8037617759-742-899835412754</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vesuv</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Vesuv detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14111,8 +14407,16 @@
           <t>1509500822-877-603392835664</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vesuv</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Vesuv detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14700,8 +15004,16 @@
           <t>6550132988-750-222659299392</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Zenix</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Zenix detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14895,8 +15207,16 @@
           <t>9999594788-502-634849415037</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lovera</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Lovera detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -15080,8 +15400,16 @@
           <t>5417650796-153-509565549653</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Posacore</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Posacore detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -15267,8 +15595,16 @@
           <t>9842322440-955-757927563926</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Orladeyo</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Orladeyo detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15864,8 +16200,16 @@
           <t>7270425970-914-679514996095</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ YUPELRI 175 mcg / 3 ml</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>YUPELRI 175 mcg / 3 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -16055,8 +16399,16 @@
           <t>6373144017-734-138521685422</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ YUPELRI 175 mcg / 3 ml</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>YUPELRI 175 mcg / 3 ml detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -16445,8 +16797,16 @@
           <t>5212023925-729-982824123831</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Betaquil</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Betaquil detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16626,8 +16986,16 @@
           <t>2571608181-804-893740087228</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Betaquil</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Betaquil detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16815,8 +17183,16 @@
           <t>2608775416-360-657340187523</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Betaquil</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Betaquil detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17000,8 +17376,16 @@
           <t>3468269056-407-594295680792</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Helt</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Helt detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -17396,8 +17780,16 @@
           <t>8695507204-426-170596634839</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Helt</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Helt detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -17788,8 +18180,16 @@
           <t>1222912233-092-302513868911</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xivar</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Xivar detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17973,8 +18373,16 @@
           <t>6549321878-010-597722806862</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Iksaront</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Iksaront detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -18166,8 +18574,16 @@
           <t>3692663762-304-169345503094</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Iksaront</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Iksaront detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -18355,8 +18771,16 @@
           <t>1941621253-892-312069999096</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Neutra</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Neutra detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -18546,8 +18970,16 @@
           <t>4430857055-874-057518699133</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Sorafenib BOS</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Sorafenib BOS detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>Boston Oncology Arabia</t>
@@ -18739,8 +19171,16 @@
           <t>3371972921-030-011594866520</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Varlin</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Varlin detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18928,8 +19368,16 @@
           <t>7019783686-903-093910436380</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Varlin  0.5 mg 11 tablets + 1 mg 14 tablets</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Varlin  0.5 mg 11 tablets + 1 mg 14 tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19119,8 +19567,16 @@
           <t>1965424103-244-009252226156</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Wetzo</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Wetzo detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
           <t>Med city</t>
@@ -19316,8 +19772,16 @@
           <t>6990752747-479-413990215080</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Wetzo 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Wetzo 10 mg 4 tablets + 20 mg 4 tablets + 30 mg 20 tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>Med city</t>

--- a/product_upload/packages/50/file.xlsx
+++ b/product_upload/packages/50/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22218,7 +22218,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22299,40 +22299,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22412,38 +22417,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>439.12</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-8B74E2AEB705</t>
         </is>
@@ -22523,38 +22533,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>278.32</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-76BC6EC4D070</t>
         </is>
@@ -22634,38 +22649,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>458.12</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-AE15549FB641</t>
         </is>
@@ -22745,38 +22765,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>327.17</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-54405044ACE2</t>
         </is>
@@ -22856,38 +22881,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>67.45</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-37BB8F1B1BFE</t>
         </is>
@@ -22967,38 +22997,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>390.09</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-A2B0DBB09876</t>
         </is>
@@ -23078,38 +23113,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>170.97</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-8F74DC9D5602</t>
         </is>
@@ -23189,38 +23229,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>225.22</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-C39DD042803C</t>
         </is>
@@ -23300,38 +23345,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>168.59</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-3301F721A47B</t>
         </is>
@@ -23411,38 +23461,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>114.42</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-5841D802C2CB</t>
         </is>
@@ -23522,38 +23577,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>224.57</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-6F556DF76845</t>
         </is>
@@ -23633,38 +23693,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>25.38</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-844359CAC3A9</t>
         </is>
@@ -23744,38 +23809,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>19.08</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-18EC095DF4EC</t>
         </is>
@@ -23855,38 +23925,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>308.61</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-A12FD4D0CA00</t>
         </is>
@@ -23966,38 +24041,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>299.03</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-CEA9A988E74D</t>
         </is>
@@ -24077,38 +24157,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>351.39</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-E112D72A2245</t>
         </is>
@@ -24188,38 +24273,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>447.13</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-69BAE6FA2FE6</t>
         </is>
@@ -24299,38 +24389,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>430.82</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-CB9386B3BFE6</t>
         </is>
@@ -24410,38 +24505,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>247.61</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-9AF661A510F3</t>
         </is>
@@ -24521,38 +24621,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>495.66</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-17E80B85E107</t>
         </is>
